--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E19C9B-6AC4-4C2A-863C-9EA0BF3BAAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA6B4F5-71FD-4DE2-8919-29CDC4B2551B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17340" yWindow="1845" windowWidth="14745" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
   <si>
     <t>enemyId</t>
   </si>
@@ -295,13 +295,6 @@
     <t>双足行走型机械</t>
   </si>
   <si>
-    <t>SpiderX</t>
-  </si>
-  <si>
-    <t>SpiderX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>移</t>
     </r>
@@ -351,6 +344,40 @@
   </si>
   <si>
     <t>Moving_coffer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPIDER X</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>スパイダ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜘蛛X</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -895,7 +922,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -903,7 +930,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -911,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -919,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -927,7 +954,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
@@ -935,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
@@ -943,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
@@ -951,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -959,7 +986,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1041,12 +1068,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -1054,7 +1081,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1141,7 +1168,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
@@ -1149,7 +1176,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA6B4F5-71FD-4DE2-8919-29CDC4B2551B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD78D77-315D-4760-A710-F7EC26098861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17340" yWindow="1845" windowWidth="14745" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <t>enemyId</t>
   </si>
@@ -378,6 +378,73 @@
   </si>
   <si>
     <t>蜘蛛X</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.boss.GoliathT</t>
+  </si>
+  <si>
+    <t>골리앗 T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.boss.GoliathT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Goliath T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ゴリアテ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>歌利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -807,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -888,9 +955,17 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -902,7 +977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -983,9 +1058,17 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -997,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -1076,11 +1159,19 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1092,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -1173,9 +1264,17 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/1. ExcelFile/EnemyDataLabel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\EnemyData\1. ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD78D77-315D-4760-A710-F7EC26098861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36357243-7AF9-4D86-AF56-EFD79FCBB620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="59">
   <si>
     <t>enemyId</t>
   </si>
@@ -444,6 +444,69 @@
         <scheme val="minor"/>
       </rPr>
       <t>T</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뮤턴트 Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mutant Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.boss.MutantZ</t>
+  </si>
+  <si>
+    <t>enemy.boss.boss.MutantZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ミュ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ータント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变异体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Z</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -452,7 +515,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,6 +596,19 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -559,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -572,6 +648,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -874,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -969,6 +1046,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -977,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -1072,6 +1157,14 @@
         <v>43</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1080,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -1175,6 +1268,14 @@
         <v>35</v>
       </c>
     </row>
+    <row r="12" spans="1:2" ht="18" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1183,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="53.19921875" bestFit="1" customWidth="1"/>
@@ -1278,6 +1379,14 @@
         <v>34</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
